--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486903_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486903_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5208</v>
+        <v>5.9659</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6184</v>
+        <v>4.8935</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9024</v>
+        <v>1.0724</v>
       </c>
       <c r="G2" t="n">
         <v>1.6317</v>
@@ -610,13 +610,13 @@
         <v>0.8214</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2916</v>
+        <v>-0.2633</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1857</v>
+        <v>-0.9106</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4773</v>
+        <v>0.6473</v>
       </c>
       <c r="V2" t="n">
         <v>3.7761</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V. MUÑOZ QUIÑONES</t>
+          <t>J. GONZALEZ ALBADALEJO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1194</v>
+        <v>5.0286</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7111</v>
+        <v>1.1574</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4082</v>
+        <v>3.8712</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6224</v>
+        <v>4.4347</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9695</v>
+        <v>0.8824</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6529</v>
+        <v>3.5523</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6347</v>
+        <v>3.2102</v>
       </c>
       <c r="K3" t="n">
-        <v>1.24</v>
+        <v>-0.71</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3947</v>
+        <v>3.9201</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9877</v>
+        <v>1.2245</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7294</v>
+        <v>1.5924</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2582</v>
+        <v>-0.3679</v>
       </c>
       <c r="P3" t="n">
-        <v>1.2321</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7845</v>
+        <v>0.0108</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0067</v>
+        <v>-0.1513</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2222</v>
+        <v>0.162</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4805</v>
+        <v>2.2259</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0698</v>
+        <v>1.1786</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5893</v>
+        <v>1.0472</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. GONZALEZ ALBADALEJO</t>
+          <t>V. MUÑOZ QUIÑONES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5774</v>
+        <v>5.0033</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0915</v>
+        <v>3.4172</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4858</v>
+        <v>1.5861</v>
       </c>
       <c r="G4" t="n">
-        <v>4.4347</v>
+        <v>2.6224</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8824</v>
+        <v>1.9695</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5523</v>
+        <v>0.6529</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2102</v>
+        <v>1.6347</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.71</v>
+        <v>1.24</v>
       </c>
       <c r="L4" t="n">
-        <v>3.9201</v>
+        <v>0.3947</v>
       </c>
       <c r="M4" t="n">
-        <v>1.2245</v>
+        <v>0.9877</v>
       </c>
       <c r="N4" t="n">
-        <v>1.5924</v>
+        <v>0.7294</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3679</v>
+        <v>0.2582</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.6427</v>
+        <v>1.2321</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4374</v>
+        <v>1.2321</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4405</v>
+        <v>0.6684</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2171</v>
+        <v>0.7127</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2233</v>
+        <v>-0.0443</v>
       </c>
       <c r="V4" t="n">
-        <v>2.2259</v>
+        <v>0.4805</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1786</v>
+        <v>1.0698</v>
       </c>
       <c r="X4" t="n">
-        <v>1.0472</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. ANDRADE AMIEL</t>
+          <t>N. REID</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.42</v>
+        <v>4.1632</v>
       </c>
       <c r="E5" t="n">
-        <v>1.155</v>
+        <v>2.195</v>
       </c>
       <c r="F5" t="n">
-        <v>2.265</v>
+        <v>1.9682</v>
       </c>
       <c r="G5" t="n">
-        <v>4.8186</v>
+        <v>3.9384</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2717</v>
+        <v>3.2016</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5469</v>
+        <v>0.7368</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5573</v>
+        <v>2.6795</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.126</v>
+        <v>1.9695</v>
       </c>
       <c r="L5" t="n">
-        <v>3.6834</v>
+        <v>0.71</v>
       </c>
       <c r="M5" t="n">
-        <v>1.2613</v>
+        <v>1.2589</v>
       </c>
       <c r="N5" t="n">
-        <v>1.3977</v>
+        <v>1.2321</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1364</v>
+        <v>0.0268</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4107</v>
+        <v>1.2321</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6427</v>
+        <v>1.2321</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1583</v>
+        <v>-0.5268</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3489</v>
+        <v>-0.4845</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1905</v>
+        <v>-0.0423</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.8295</v>
+        <v>-0.4805</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8295</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. REID</t>
+          <t>F. ANDRADE AMIEL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.3314</v>
+        <v>3.6375</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5015</v>
+        <v>1.6393</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8299</v>
+        <v>1.9982</v>
       </c>
       <c r="G6" t="n">
-        <v>3.9384</v>
+        <v>4.8186</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2016</v>
+        <v>1.2717</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7368</v>
+        <v>3.5469</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6795</v>
+        <v>3.5573</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9695</v>
+        <v>-0.126</v>
       </c>
       <c r="L6" t="n">
-        <v>0.71</v>
+        <v>3.6834</v>
       </c>
       <c r="M6" t="n">
-        <v>1.2589</v>
+        <v>1.2613</v>
       </c>
       <c r="N6" t="n">
-        <v>1.2321</v>
+        <v>1.3977</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0268</v>
+        <v>-0.1364</v>
       </c>
       <c r="P6" t="n">
-        <v>1.2321</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2321</v>
+        <v>1.6427</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3586</v>
+        <v>0.0592</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.178</v>
+        <v>0.1354</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1806</v>
+        <v>-0.0762</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4805</v>
+        <v>-0.8295</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4805</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. AGUILAR HERNANDEZ</t>
+          <t>J. HIERREZUELO SERER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.0987</v>
+        <v>3.2576</v>
       </c>
       <c r="E7" t="n">
-        <v>4.459</v>
+        <v>2.2924</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3603</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>5.865</v>
+        <v>2.8981</v>
       </c>
       <c r="H7" t="n">
-        <v>3.7469</v>
+        <v>0.4539</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1181</v>
+        <v>2.4442</v>
       </c>
       <c r="J7" t="n">
-        <v>6.3455</v>
+        <v>2.8078</v>
       </c>
       <c r="K7" t="n">
-        <v>2.7676</v>
+        <v>-0.1912</v>
       </c>
       <c r="L7" t="n">
-        <v>3.578</v>
+        <v>2.999</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4806</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9792999999999999</v>
+        <v>0.6452</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4599</v>
+        <v>-0.5548</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.616</v>
+        <v>0.8214</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4374</v>
+        <v>0.8214</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3823</v>
+        <v>-0.4619</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4225</v>
+        <v>-0.5154</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0402</v>
+        <v>0.0535</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.7679</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.3573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. HIERREZUELO SERER</t>
+          <t>V. AGUILAR HERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.7157</v>
+        <v>3.0617</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0173</v>
+        <v>4.6294</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6984</v>
+        <v>-1.5678</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8981</v>
+        <v>5.865</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4539</v>
+        <v>3.7469</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4442</v>
+        <v>2.1181</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8078</v>
+        <v>6.3455</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1912</v>
+        <v>2.7676</v>
       </c>
       <c r="L8" t="n">
-        <v>2.999</v>
+        <v>3.578</v>
       </c>
       <c r="M8" t="n">
-        <v>0.09030000000000001</v>
+        <v>-0.4806</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6452</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5548</v>
+        <v>-1.4599</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8214</v>
+        <v>-0.616</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8214</v>
+        <v>1.4374</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0038</v>
+        <v>-0.4193</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7905</v>
+        <v>-0.252</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2133</v>
+        <v>-0.1673</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.7679</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.7806</v>
+        <v>1.8974</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1126</v>
+        <v>0.9034</v>
       </c>
       <c r="F9" t="n">
-        <v>0.668</v>
+        <v>0.9941</v>
       </c>
       <c r="G9" t="n">
         <v>1.2064</v>
@@ -1156,13 +1156,13 @@
         <v>0.8214</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5963000000000001</v>
+        <v>-0.4794</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0931</v>
+        <v>-0.3023</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5032</v>
+        <v>-0.1771</v>
       </c>
       <c r="V9" t="n">
         <v>0.3491</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1992</v>
+        <v>-0.1128</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7702</v>
+        <v>1.7973</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9694</v>
+        <v>-1.9101</v>
       </c>
       <c r="G10" t="n">
         <v>0.1952</v>
@@ -1234,13 +1234,13 @@
         <v>0.616</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.224</v>
+        <v>-0.1375</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1781</v>
+        <v>0.2052</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4021</v>
+        <v>-0.3428</v>
       </c>
       <c r="V10" t="n">
         <v>0.2402</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5488</v>
+        <v>-3.3783</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2897</v>
+        <v>-2.1192</v>
       </c>
       <c r="F11" t="n">
         <v>-1.2591</v>
@@ -1312,10 +1312,10 @@
         <v>0.2053</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1976</v>
+        <v>-0.0271</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1976</v>
+        <v>-0.0271</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>27.816</v>
+        <v>28.5241</v>
       </c>
       <c r="E12" t="n">
-        <v>20.1469</v>
+        <v>20.8057</v>
       </c>
       <c r="F12" t="n">
-        <v>7.668899999999999</v>
+        <v>7.718399999999999</v>
       </c>
       <c r="G12" t="n">
         <v>24.5345</v>
@@ -1366,7 +1366,7 @@
         <v>21.9872</v>
       </c>
       <c r="K12" t="n">
-        <v>6.216100000000001</v>
+        <v>6.2161</v>
       </c>
       <c r="L12" t="n">
         <v>15.771</v>
@@ -1390,19 +1390,19 @@
         <v>10.2672</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.2853</v>
+        <v>-1.5769</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.2486</v>
+        <v>-1.5899</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.03669999999999984</v>
+        <v>0.01279999999999998</v>
       </c>
       <c r="V12" t="n">
-        <v>3.5134</v>
+        <v>3.513400000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>8.622000000000002</v>
+        <v>8.622</v>
       </c>
       <c r="X12" t="n">
         <v>-5.108700000000001</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. CADME ARIAS</t>
+          <t>J. TAVELLI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4105</v>
+        <v>1.5801</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1413</v>
+        <v>2.2886</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7308</v>
+        <v>-0.7084</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.392</v>
+        <v>1.6784</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.9762999999999999</v>
+        <v>-1.0317</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4157</v>
+        <v>2.7101</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1622</v>
+        <v>3.9009</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.4798</v>
       </c>
       <c r="L13" t="n">
-        <v>0.697</v>
+        <v>4.3807</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.5542</v>
+        <v>-2.2225</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4415</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1127</v>
+        <v>-1.6706</v>
       </c>
       <c r="P13" t="n">
-        <v>0.8214</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8214</v>
+        <v>1.0267</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5007</v>
+        <v>0.2508</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4987</v>
+        <v>-0.2365</v>
       </c>
       <c r="U13" t="n">
-        <v>0.002</v>
+        <v>0.4873</v>
       </c>
       <c r="V13" t="n">
-        <v>0.4805</v>
+        <v>-0.3491</v>
       </c>
       <c r="W13" t="n">
-        <v>0.4805</v>
+        <v>-0.3491</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. TAVELLI</t>
+          <t>G. CADME ARIAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.425</v>
+        <v>0.7805</v>
       </c>
       <c r="E14" t="n">
-        <v>2.184</v>
+        <v>1.3631</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.759</v>
+        <v>-0.5826</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6784</v>
+        <v>-1.392</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.0317</v>
+        <v>-0.9762999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7101</v>
+        <v>-0.4157</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9009</v>
+        <v>0.1622</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.4798</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>4.3807</v>
+        <v>0.697</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.2225</v>
+        <v>-1.5542</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.4415</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.6706</v>
+        <v>-1.1127</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.8214</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.0267</v>
+        <v>0.8214</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0956</v>
+        <v>0.8707</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3411</v>
+        <v>0.7204</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4368</v>
+        <v>0.1502</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3491</v>
+        <v>0.4805</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3491</v>
+        <v>0.4805</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2037</v>
+        <v>0.4286</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4072</v>
+        <v>3.721</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.2035</v>
+        <v>-3.2924</v>
       </c>
       <c r="G15" t="n">
         <v>0.5118</v>
@@ -1624,13 +1624,13 @@
         <v>0.4107</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2197</v>
+        <v>0.4445</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3566</v>
+        <v>-0.0428</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5763</v>
+        <v>0.4873</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9384</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. GARCIA ROSELLO</t>
+          <t>F. HERNANDEZ MARTINEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.1348</v>
+        <v>-0.4284</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7425</v>
+        <v>0.6906</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3923</v>
+        <v>-1.119</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8535</v>
+        <v>-2.2612</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.1474</v>
+        <v>-2.9165</v>
       </c>
       <c r="I16" t="n">
-        <v>1.294</v>
+        <v>0.6552</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6572</v>
+        <v>0.4188</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.4852</v>
+        <v>-1.9753</v>
       </c>
       <c r="L16" t="n">
-        <v>0.828</v>
+        <v>2.394</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1963</v>
+        <v>-2.68</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6623</v>
+        <v>-0.9412</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4659</v>
+        <v>-1.7388</v>
       </c>
       <c r="P16" t="n">
-        <v>0.616</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R16" t="n">
-        <v>0.616</v>
+        <v>0.8214</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5215</v>
+        <v>0.2702</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0854</v>
+        <v>-0.1204</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6069</v>
+        <v>0.3905</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.4189</v>
+        <v>1.7679</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4189</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. HERNANDEZ MARTINEZ</t>
+          <t>M. GARCIA ROSELLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.6354</v>
+        <v>-0.9046999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5647</v>
+        <v>-0.5333</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0707</v>
+        <v>-0.3714</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.2612</v>
+        <v>-0.8535</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.9165</v>
+        <v>-2.1474</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6552</v>
+        <v>1.294</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4188</v>
+        <v>-0.6572</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.9753</v>
+        <v>-1.4852</v>
       </c>
       <c r="L17" t="n">
-        <v>2.394</v>
+        <v>0.828</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.68</v>
+        <v>-0.1963</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9412</v>
+        <v>-0.6623</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.7388</v>
+        <v>0.4659</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8214</v>
+        <v>0.616</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9368</v>
+        <v>0.7516</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3756</v>
+        <v>0.1238</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4388</v>
+        <v>0.6278</v>
       </c>
       <c r="V17" t="n">
-        <v>1.7679</v>
+        <v>-1.4189</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3491</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.7225</v>
+        <v>-2.7941</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7791</v>
+        <v>-0.4653</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9434</v>
+        <v>-2.3288</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7149</v>
@@ -1858,13 +1858,13 @@
         <v>0.616</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8938</v>
+        <v>0.8223</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.07770000000000001</v>
+        <v>0.2361</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9715</v>
+        <v>0.5861</v>
       </c>
       <c r="V18" t="n">
         <v>0.5893</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.9835</v>
+        <v>-3.3287</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6742</v>
+        <v>-1.1972</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.3093</v>
+        <v>-2.1314</v>
       </c>
       <c r="G19" t="n">
         <v>-3.0973</v>
@@ -1936,13 +1936,13 @@
         <v>0.2053</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8468</v>
+        <v>0.5017</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9413</v>
+        <v>0.4183</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0945</v>
+        <v>0.0834</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9384</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.6255</v>
+        <v>-3.7858</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7758</v>
+        <v>-1.1942</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.8497</v>
+        <v>-2.5917</v>
       </c>
       <c r="G20" t="n">
         <v>-4.7117</v>
@@ -2014,13 +2014,13 @@
         <v>0.616</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4702</v>
+        <v>0.3098</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2245</v>
+        <v>-0.1939</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2458</v>
+        <v>0.5038</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.1594</v>
+        <v>-5.1018</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0751</v>
+        <v>-2.2843</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.0843</v>
+        <v>-2.8175</v>
       </c>
       <c r="G21" t="n">
         <v>-3.1434</v>
@@ -2092,13 +2092,13 @@
         <v>0.8214</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3918</v>
+        <v>-0.3342</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3408</v>
+        <v>0.1315</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7326</v>
+        <v>-0.4658</v>
       </c>
       <c r="V21" t="n">
         <v>-1.4189</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.9631</v>
+        <v>-5.5761</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.3969</v>
+        <v>-5.1877</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5662</v>
+        <v>-0.3884</v>
       </c>
       <c r="G22" t="n">
         <v>-3.8806</v>
@@ -2170,13 +2170,13 @@
         <v>1.2321</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.2848</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3489</v>
+        <v>-0.1397</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.323</v>
+        <v>-0.1452</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5893</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.631</v>
+        <v>-7.9389</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.3932</v>
+        <v>-4.8702</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.2378</v>
+        <v>-3.0687</v>
       </c>
       <c r="G23" t="n">
         <v>-6.6701</v>
@@ -2248,13 +2248,13 @@
         <v>1.0267</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2627</v>
+        <v>-0.5706</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.3833</v>
+        <v>-0.8603</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1206</v>
+        <v>0.2897</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6982</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-27.816</v>
+        <v>-27.0693</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.669</v>
+        <v>-7.6689</v>
       </c>
       <c r="F24" t="n">
-        <v>-20.147</v>
+        <v>-19.4003</v>
       </c>
       <c r="G24" t="n">
         <v>-24.5345</v>
@@ -2299,7 +2299,7 @@
         <v>-8.9468</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.547299999999999</v>
+        <v>-2.547299999999998</v>
       </c>
       <c r="K24" t="n">
         <v>-9.371700000000001</v>
@@ -2326,13 +2326,13 @@
         <v>8.213699999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>2.285100000000001</v>
+        <v>3.032</v>
       </c>
       <c r="T24" t="n">
-        <v>0.03669999999999995</v>
+        <v>0.03650000000000031</v>
       </c>
       <c r="U24" t="n">
-        <v>2.2486</v>
+        <v>2.9951</v>
       </c>
       <c r="V24" t="n">
         <v>-3.5135</v>
